--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>4.77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>4.91</v>
+        <v>5.51</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P18" t="n">
-        <v>5.51</v>
+        <v>4.91</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>4.77</v>
+        <v>2.72</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="O14" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="P14" t="n">
-        <v>4.67</v>
+        <v>4.91</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>5.51</v>
+        <v>3.82</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P17" t="n">
-        <v>3.82</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="O18" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P18" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="P19" t="n">
-        <v>2.72</v>
+        <v>5.51</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="P13" t="n">
-        <v>4.77</v>
+        <v>4.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="P14" t="n">
-        <v>4.91</v>
+        <v>5.51</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="O16" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="P16" t="n">
-        <v>4.12</v>
+        <v>4.67</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O19" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P19" t="n">
-        <v>5.51</v>
+        <v>4.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="O14" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>5.51</v>
+        <v>2.72</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P15" t="n">
-        <v>3.82</v>
+        <v>4.67</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.68</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>4.67</v>
+        <v>5.51</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="O17" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>3.82</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="O13" t="n">
-        <v>3.72</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>4.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.72</v>
+        <v>3.82</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.68</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>4.67</v>
+        <v>5.51</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.51</v>
+        <v>4.77</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P17" t="n">
-        <v>3.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P18" t="n">
-        <v>4.77</v>
+        <v>4.67</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.34</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>5.51</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P14" t="n">
-        <v>3.82</v>
+        <v>4.91</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>5.51</v>
+        <v>2.72</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="P16" t="n">
-        <v>4.77</v>
+        <v>4.12</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.12</v>
+        <v>4.77</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>4.91</v>
+        <v>3.82</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.72</v>
       </c>
       <c r="P13" t="n">
-        <v>5.51</v>
+        <v>4.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="P14" t="n">
-        <v>4.91</v>
+        <v>5.51</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="O15" t="n">
-        <v>3.18</v>
+        <v>3.68</v>
       </c>
       <c r="P15" t="n">
-        <v>2.72</v>
+        <v>4.67</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="O16" t="n">
-        <v>3.72</v>
+        <v>3.18</v>
       </c>
       <c r="P16" t="n">
-        <v>4.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="O18" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>4.67</v>
+        <v>3.82</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P19" t="n">
-        <v>3.82</v>
+        <v>4.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O13" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>4.12</v>
+        <v>4.77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="O15" t="n">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>4.67</v>
+        <v>2.72</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="O16" t="n">
-        <v>3.18</v>
+        <v>3.68</v>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>4.67</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>4.77</v>
+        <v>3.82</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P18" t="n">
-        <v>3.82</v>
+        <v>4.91</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P19" t="n">
-        <v>4.91</v>
+        <v>4.12</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>4.77</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>4.55</v>
+        <v>3.72</v>
       </c>
       <c r="P14" t="n">
-        <v>5.51</v>
+        <v>4.12</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.72</v>
+        <v>4.77</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="O16" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>4.67</v>
+        <v>3.82</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P17" t="n">
-        <v>3.82</v>
+        <v>5.51</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="O18" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P18" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="O19" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="P19" t="n">
-        <v>4.12</v>
+        <v>4.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.72</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>4.12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="P14" t="n">
-        <v>4.12</v>
+        <v>5.51</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.77</v>
+        <v>3.82</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P16" t="n">
-        <v>3.82</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>5.51</v>
+        <v>4.77</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="O18" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="P18" t="n">
-        <v>4.67</v>
+        <v>4.91</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P19" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="O13" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="P13" t="n">
-        <v>4.12</v>
+        <v>4.91</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>4.55</v>
+        <v>3.72</v>
       </c>
       <c r="P14" t="n">
-        <v>5.51</v>
+        <v>4.12</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>3.82</v>
+        <v>5.51</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="O16" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>3.82</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P17" t="n">
-        <v>4.77</v>
+        <v>4.67</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>4.91</v>
+        <v>4.77</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>4.67</v>
+        <v>2.72</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="P14" t="n">
-        <v>4.12</v>
+        <v>5.51</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>5.51</v>
+        <v>3.82</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P16" t="n">
-        <v>3.82</v>
+        <v>4.67</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="P17" t="n">
-        <v>4.67</v>
+        <v>4.12</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.54</v>
+        <v>2.34</v>
       </c>
       <c r="O13" t="n">
-        <v>4.05</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>4.91</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O14" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P14" t="n">
-        <v>5.51</v>
+        <v>4.91</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>3.82</v>
+        <v>5.51</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="O17" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>4.12</v>
+        <v>3.82</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P18" t="n">
-        <v>4.77</v>
+        <v>4.67</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.18</v>
+        <v>3.72</v>
       </c>
       <c r="P19" t="n">
-        <v>2.72</v>
+        <v>4.12</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.82</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P14" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P15" t="n">
-        <v>5.51</v>
+        <v>4.91</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P17" t="n">
-        <v>3.82</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.68</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>4.67</v>
+        <v>5.51</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>3.82</v>
+        <v>5.51</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.18</v>
+        <v>3.72</v>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>4.12</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>5.51</v>
+        <v>3.82</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>3.72</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>4.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1052,55 +1052,55 @@
         <v>2.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P11" t="n">
-        <v>3.79</v>
+        <v>2.87</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="O14" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="P14" t="n">
-        <v>4.67</v>
+        <v>4.91</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="O15" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P15" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>4.77</v>
+        <v>3.82</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P18" t="n">
-        <v>3.82</v>
+        <v>2.72</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.72</v>
+        <v>4.77</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P14" t="n">
-        <v>4.91</v>
+        <v>4.12</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P16" t="n">
-        <v>3.82</v>
+        <v>4.91</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="O17" t="n">
-        <v>3.72</v>
+        <v>3.18</v>
       </c>
       <c r="P17" t="n">
-        <v>4.12</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="O18" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.72</v>
+        <v>3.82</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>4.12</v>
+        <v>3.82</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>4.77</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P18" t="n">
-        <v>3.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>4.77</v>
+        <v>2.72</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>2.87</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>2.87</v>
+        <v>3.79</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>5.51</v>
+        <v>3.82</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.82</v>
+        <v>2.72</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="O16" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P16" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P17" t="n">
-        <v>4.77</v>
+        <v>4.91</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="P19" t="n">
-        <v>2.72</v>
+        <v>5.51</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>2.87</v>
+        <v>3.79</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P11" t="n">
-        <v>3.79</v>
+        <v>2.87</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>5.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P13" t="n">
-        <v>3.82</v>
+        <v>4.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.68</v>
       </c>
       <c r="P14" t="n">
-        <v>2.72</v>
+        <v>4.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="P15" t="n">
-        <v>4.77</v>
+        <v>4.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="O16" t="n">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="P16" t="n">
-        <v>4.67</v>
+        <v>2.72</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,31 +3110,31 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.91</v>
+        <v>4.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>4.12</v>
+        <v>5.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>5.51</v>
+        <v>3.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P13" t="n">
-        <v>4.91</v>
+        <v>4.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U13" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.17</v>
+        <v>3.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="O15" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="P15" t="n">
-        <v>4.12</v>
+        <v>4.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.57</v>
+        <v>4.17</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>4.77</v>
+        <v>3.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S17" t="n">
         <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3.15</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
         <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>5.51</v>
+        <v>4.77</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.95</v>
+        <v>3.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.21</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P19" t="n">
-        <v>3.82</v>
+        <v>5.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="R19" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="S19" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>2.79</v>
+        <v>2.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>2.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.15</v>
+        <v>2.21</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>4.12</v>
+        <v>5.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="S13" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="T13" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.57</v>
+        <v>4.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.1</v>
+        <v>2.21</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="O14" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>4.67</v>
+        <v>3.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T14" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="U14" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
         <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="O15" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>4.91</v>
+        <v>4.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.3</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z15" t="n">
-        <v>4.17</v>
+        <v>3.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="O16" t="n">
-        <v>3.18</v>
+        <v>3.68</v>
       </c>
       <c r="P16" t="n">
-        <v>2.72</v>
+        <v>4.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P17" t="n">
-        <v>3.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="R17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
         <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="U17" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
         <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK17" t="n">
         <v>2</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.74</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,31 +3269,31 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="P18" t="n">
-        <v>4.77</v>
+        <v>2.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="O19" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P19" t="n">
-        <v>5.51</v>
+        <v>4.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="V19" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.15</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.68</v>
       </c>
       <c r="P13" t="n">
-        <v>5.51</v>
+        <v>4.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="R13" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.23</v>
       </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P14" t="n">
-        <v>3.82</v>
+        <v>4.91</v>
       </c>
       <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
         <v>2.3</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.15</v>
-      </c>
       <c r="S14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>2.79</v>
+        <v>2.41</v>
       </c>
       <c r="V14" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>4.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,31 +2792,31 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>4.77</v>
+        <v>2.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2825,31 +2825,31 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.68</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>4.67</v>
+        <v>5.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T16" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>2.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.12</v>
+        <v>4.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
         <v>2.2</v>
@@ -3128,47 +3128,47 @@
         <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.57</v>
+        <v>3.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG17" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.18</v>
+        <v>3.72</v>
       </c>
       <c r="P18" t="n">
-        <v>2.72</v>
+        <v>4.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>4.91</v>
+        <v>3.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U19" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.17</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.74</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1052,22 +1052,22 @@
         <v>2.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="S4" t="n">
         <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.55</v>
+        <v>3.36</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="V4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
         <v>1.11</v>
@@ -1079,19 +1079,19 @@
         <v>1.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC4" t="n">
         <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE4" t="n">
         <v>1.24</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="O13" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
         <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.08</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.18</v>
+        <v>3.72</v>
       </c>
       <c r="P15" t="n">
-        <v>2.72</v>
+        <v>4.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="O16" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>5.51</v>
+        <v>3.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="V16" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.95</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.67</v>
+        <v>1.87</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.21</v>
+        <v>3.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.77</v>
+        <v>5.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>3.64</v>
       </c>
       <c r="U17" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.15</v>
+        <v>4.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.96</v>
+        <v>1.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="P18" t="n">
-        <v>4.12</v>
+        <v>4.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="R18" t="n">
         <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T18" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="U18" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
         <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
         <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P19" t="n">
-        <v>3.82</v>
+        <v>2.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3593,25 +3593,25 @@
         <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -3620,31 +3620,31 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>4.77</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P14" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.3</v>
       </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="AE14" t="n">
         <v>1.11</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="O15" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="P15" t="n">
-        <v>4.12</v>
+        <v>4.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.57</v>
+        <v>4.17</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P16" t="n">
-        <v>3.82</v>
+        <v>4.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="R16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
         <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="U16" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
         <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>3.57</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK16" t="n">
         <v>2</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>5.6</v>
+        <v>3.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="S17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.22</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z17" t="n">
-        <v>4.95</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.7</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.19</v>
+        <v>3.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="O18" t="n">
-        <v>3.68</v>
+        <v>4.6</v>
       </c>
       <c r="P18" t="n">
-        <v>4.67</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="S18" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.78</v>
+        <v>3.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,31 +3428,31 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.72</v>
+        <v>4.77</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3461,31 +3461,31 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>3.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="O14" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="R14" t="n">
         <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.08</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P15" t="n">
-        <v>4.91</v>
+        <v>4.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.17</v>
+        <v>3.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="O16" t="n">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>4.12</v>
+        <v>5.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>3.08</v>
+        <v>3.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.57</v>
+        <v>4.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.82</v>
+        <v>1.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P17" t="n">
-        <v>3.82</v>
+        <v>4.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="R17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="U17" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
         <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.49</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>3.18</v>
       </c>
       <c r="P18" t="n">
-        <v>5.6</v>
+        <v>2.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P19" t="n">
-        <v>4.77</v>
+        <v>4.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK19" t="n">
         <v>2.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.96</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1052,7 +1052,7 @@
         <v>2.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.84</v>
+        <v>3.14</v>
       </c>
       <c r="R4" t="n">
         <v>2.27</v>
@@ -1061,37 +1061,37 @@
         <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.36</v>
+        <v>3.55</v>
       </c>
       <c r="U4" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
         <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
         <v>1.24</v>
@@ -1100,7 +1100,7 @@
         <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.53</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AK8" t="n">
         <v>1.24</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>2.12</v>
       </c>
       <c r="AK9" t="n">
         <v>1.1</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="P10" t="n">
-        <v>3.79</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P12" t="n">
-        <v>5.89</v>
+        <v>6.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>4.24</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
         <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>3.82</v>
+        <v>5.3</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2.3</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.71</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>4.77</v>
+        <v>3.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="P15" t="n">
-        <v>4.12</v>
+        <v>4.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.93</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AC16" t="n">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,31 +3110,31 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="O17" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>4.67</v>
+        <v>4.47</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
         <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
         <v>2.78</v>
       </c>
       <c r="U17" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
         <v>1.08</v>
@@ -3143,19 +3143,19 @@
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD17" t="n">
         <v>1.3</v>
@@ -3167,7 +3167,7 @@
         <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="P19" t="n">
-        <v>4.91</v>
+        <v>5.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U19" t="n">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.11</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK19" t="n">
         <v>2.2</v>
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P20" t="n">
-        <v>2.86</v>
+        <v>2.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
         <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
         <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
         <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.22</v>
       </c>
       <c r="P13" t="n">
-        <v>5.3</v>
+        <v>3.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.52</v>
       </c>
       <c r="O14" t="n">
-        <v>3.22</v>
+        <v>3.92</v>
       </c>
       <c r="P14" t="n">
-        <v>3.01</v>
+        <v>5.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.3</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>3.8</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.44</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.33</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="AE17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.91</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK18" t="n">
         <v>2</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.83</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>5.83</v>
+        <v>4.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="U19" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="V19" t="n">
         <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
         <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.01</v>
+        <v>4.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="O14" t="n">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>5.83</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
         <v>1.35</v>
       </c>
       <c r="T14" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="U14" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK14" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="P15" t="n">
-        <v>3.5</v>
+        <v>5.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S15" t="n">
         <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="O16" t="n">
-        <v>4.55</v>
+        <v>3.22</v>
       </c>
       <c r="P16" t="n">
-        <v>5.3</v>
+        <v>3.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T17" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="U17" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.11</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S18" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>3.02</v>
+        <v>3.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.44</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.33</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA19" t="n">
+      <c r="AE19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.19</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.22</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>3.01</v>
+        <v>5.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>3.01</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T18" t="n">
-        <v>3.8</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1043,34 +1043,34 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="P4" t="n">
-        <v>2.59</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="R4" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="V4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
@@ -1079,28 +1079,28 @@
         <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1679,37 +1679,37 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
         <v>1.22</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
         <v>1.1</v>
@@ -2156,25 +2156,25 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="P11" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S11" t="n">
         <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
         <v>2.33</v>
@@ -2183,7 +2183,7 @@
         <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -2192,13 +2192,13 @@
         <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
         <v>2.7</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
         <v>1.64</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.25</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="O16" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T16" t="n">
-        <v>3.8</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="V16" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z18" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AA18" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.6</v>
+        <v>2.19</v>
       </c>
       <c r="O19" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="P19" t="n">
-        <v>4.4</v>
+        <v>3.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>3.39</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.39</v>
+        <v>2.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.34</v>
+        <v>1.84</v>
       </c>
       <c r="O10" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>3.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.68</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="V11" t="n">
         <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="O12" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P12" t="n">
-        <v>6.84</v>
+        <v>6.9</v>
       </c>
       <c r="Q12" t="n">
         <v>1.85</v>
@@ -2330,16 +2330,16 @@
         <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.09</v>
@@ -2348,28 +2348,28 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
         <v>1.91</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>4.47</v>
+        <v>5.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.2</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.8</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>5.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="O14" t="n">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="R14" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,61 +2792,61 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.52</v>
+        <v>2.09</v>
       </c>
       <c r="O15" t="n">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>5.83</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.13</v>
+        <v>2.67</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="U15" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
         <v>1.85</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
-        <v>3.5</v>
+        <v>5.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V17" t="n">
         <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="P18" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.1</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T18" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U18" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.11</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.19</v>
+        <v>1.56</v>
       </c>
       <c r="O19" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="P19" t="n">
-        <v>3.01</v>
+        <v>4.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="P20" t="n">
         <v>2.55</v>
@@ -3602,10 +3602,10 @@
         <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U20" t="n">
         <v>2.99</v>
@@ -3626,10 +3626,10 @@
         <v>2.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
         <v>3.6</v>
@@ -3641,10 +3641,10 @@
         <v>1.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>6.9</v>
+        <v>6.64</v>
       </c>
       <c r="Q12" t="n">
         <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S12" t="n">
         <v>1.31</v>
@@ -2336,13 +2336,13 @@
         <v>3.15</v>
       </c>
       <c r="U12" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="V12" t="n">
         <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
@@ -2366,7 +2366,7 @@
         <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
         <v>1.84</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.74</v>
       </c>
       <c r="P13" t="n">
-        <v>5.51</v>
+        <v>4.36</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.95</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="AC13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z13" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2.09</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.9</v>
+        <v>2.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>4.55</v>
       </c>
       <c r="P17" t="n">
-        <v>5.73</v>
+        <v>5.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="S17" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.12</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="O18" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>4.36</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.23</v>
+        <v>2.67</v>
       </c>
       <c r="R18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.1</v>
       </c>
-      <c r="S18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="O19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>4.75</v>
+        <v>5.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="U19" t="n">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.11</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="P20" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="Q20" t="n">
         <v>3.1</v>
@@ -3605,7 +3605,7 @@
         <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
         <v>2.99</v>
@@ -3623,7 +3623,7 @@
         <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AA20" t="n">
         <v>2.05</v>
@@ -3632,19 +3632,19 @@
         <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O22" t="n">
         <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="R22" t="n">
         <v>2</v>
@@ -3923,13 +3923,13 @@
         <v>1.49</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="U22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
         <v>1.01</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="O13" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.36</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.23</v>
+        <v>2.67</v>
       </c>
       <c r="R13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.1</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="P15" t="n">
-        <v>4.75</v>
+        <v>4.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.11</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,65 +3110,65 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>5.51</v>
+        <v>4.5</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.95</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>5.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="R18" t="n">
-        <v>2.01</v>
+        <v>2.63</v>
       </c>
       <c r="S18" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>3.58</v>
       </c>
       <c r="U18" t="n">
-        <v>3.08</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>2.42</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="O22" t="n">
         <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
         <v>1.49</v>
@@ -3926,7 +3926,7 @@
         <v>2.41</v>
       </c>
       <c r="U22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V22" t="n">
         <v>1.28</v>
@@ -3950,13 +3950,13 @@
         <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AD22" t="n">
         <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF22" t="n">
         <v>1.95</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.09</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.67</v>
-      </c>
       <c r="R13" t="n">
-        <v>2.01</v>
+        <v>2.36</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.9</v>
+        <v>3.12</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.56</v>
+        <v>2.09</v>
       </c>
       <c r="O14" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>2.67</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="U14" t="n">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>3.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="O15" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="P15" t="n">
-        <v>4.36</v>
+        <v>4.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>3.74</v>
       </c>
       <c r="P18" t="n">
-        <v>5.51</v>
+        <v>4.36</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.95</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>4.55</v>
       </c>
       <c r="P19" t="n">
-        <v>5.73</v>
+        <v>5.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="S19" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>2.85</v>
+        <v>3.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.12</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3911,13 +3911,13 @@
         <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S22" t="n">
         <v>1.49</v>
@@ -3929,7 +3929,7 @@
         <v>3.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
         <v>1.01</v>
@@ -3938,19 +3938,19 @@
         <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB22" t="n">
         <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
         <v>1.16</v>
@@ -3959,7 +3959,7 @@
         <v>1.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG22" t="n">
         <v>1.75</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK22" t="n">
         <v>1.8</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1049,37 +1049,37 @@
         <v>3.47</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S4" t="n">
         <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.75</v>
+        <v>4.98</v>
       </c>
       <c r="AA4" t="n">
         <v>1.57</v>
@@ -1088,19 +1088,19 @@
         <v>2.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF4" t="n">
         <v>1.45</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AK4" t="n">
         <v>1.44</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.39</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.56</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.84</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="P10" t="n">
-        <v>3.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>3.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD11" t="n">
         <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>4.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
         <v>2.1</v>
@@ -2372,7 +2372,7 @@
         <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
-        <v>5.73</v>
+        <v>5.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>3.58</v>
       </c>
       <c r="U13" t="n">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.12</v>
+        <v>2.26</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,16 +2633,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
         <v>3.2</v>
       </c>
       <c r="P14" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2.9</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.67</v>
       </c>
       <c r="R14" t="n">
         <v>2.01</v>
@@ -2666,16 +2666,16 @@
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
         <v>3.9</v>
@@ -2684,13 +2684,13 @@
         <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,25 +2951,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="U16" t="n">
         <v>2.66</v>
@@ -2978,53 +2978,53 @@
         <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK16" t="n">
         <v>2</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>3.92</v>
       </c>
       <c r="P17" t="n">
-        <v>4.5</v>
+        <v>4.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S17" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AK17" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>4.36</v>
+        <v>4.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T18" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="U18" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
         <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
         <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O19" t="n">
-        <v>4.55</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>5.51</v>
+        <v>5.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R19" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="T19" t="n">
-        <v>3.58</v>
+        <v>2.85</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="V19" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK19" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T20" t="n">
         <v>2.65</v>
@@ -3617,7 +3617,7 @@
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
         <v>1.3</v>
@@ -3635,10 +3635,10 @@
         <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF20" t="n">
         <v>1.75</v>
@@ -3660,7 +3660,7 @@
         <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="O21" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="P21" t="n">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -725,43 +725,43 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA2" t="n">
         <v>1.8</v>
@@ -770,19 +770,19 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.52</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P14" t="n">
-        <v>3.03</v>
+        <v>5.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="R14" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T14" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.66</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="AB16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.1</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AF16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.59</v>
+        <v>2.19</v>
       </c>
       <c r="O17" t="n">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>4.81</v>
+        <v>3.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>2.01</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="T17" t="n">
-        <v>3.12</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>2.41</v>
+        <v>3.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.66</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.56</v>
+        <v>3.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
         <v>1.9</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,34 +3428,34 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="O19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P19" t="n">
         <v>3.9</v>
       </c>
-      <c r="P19" t="n">
-        <v>5.65</v>
-      </c>
       <c r="Q19" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S19" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="U19" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="V19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
@@ -3464,28 +3464,28 @@
         <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD19" t="n">
         <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>3.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="O11" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="P11" t="n">
-        <v>3.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.5</v>
       </c>
-      <c r="O13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P13" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.95</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>5.65</v>
+        <v>5.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="S14" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>3.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="U15" t="n">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,61 +2951,61 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.59</v>
+        <v>2.19</v>
       </c>
       <c r="O16" t="n">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>4.81</v>
+        <v>3.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="R16" t="n">
-        <v>2.31</v>
+        <v>2.01</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>2.73</v>
       </c>
       <c r="U16" t="n">
-        <v>2.41</v>
+        <v>3.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.66</v>
       </c>
-      <c r="AB16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AC16" t="n">
-        <v>2.56</v>
+        <v>3.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
         <v>1.9</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.19</v>
+        <v>1.52</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
-        <v>3.03</v>
+        <v>5.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.2</v>
       </c>
       <c r="S18" t="n">
         <v>1.35</v>
       </c>
       <c r="T18" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AB18" t="n">
         <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
         <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,34 +3428,34 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q19" t="n">
         <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T19" t="n">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="U19" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
@@ -3464,28 +3464,28 @@
         <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
         <v>1.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
         <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.74</v>
       </c>
-      <c r="O7" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="P10" t="n">
-        <v>3.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>3.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>4.81</v>
+        <v>3.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U13" t="n">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.5</v>
       </c>
-      <c r="O14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="W14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.95</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.6</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.57</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,34 +3110,34 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>5.65</v>
+        <v>4.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="U17" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
@@ -3146,28 +3146,28 @@
         <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB17" t="n">
         <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
         <v>2.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T18" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="U18" t="n">
-        <v>2.43</v>
+        <v>2.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
         <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>4.5</v>
+        <v>5.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="R19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.2</v>
       </c>
-      <c r="S19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.75</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.81</v>
+        <v>1.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.81</v>
+        <v>3.19</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="S2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>2.7</v>
@@ -779,10 +779,10 @@
         <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK2" t="n">
         <v>1.2</v>
@@ -1049,58 +1049,58 @@
         <v>3.47</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="Q4" t="n">
         <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.98</v>
+        <v>4.75</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.87</v>
+        <v>3.96</v>
       </c>
       <c r="R7" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
         <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
         <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
         <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AK7" t="n">
         <v>1.24</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
         <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>6.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.53</v>
       </c>
-      <c r="Q9" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
         <v>1.69</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>2.43</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
         <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="U10" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.68</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
         <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
         <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
@@ -2189,19 +2189,19 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.85</v>
+        <v>4.57</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
         <v>1.44</v>
@@ -2210,10 +2210,10 @@
         <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P12" t="n">
         <v>6.64</v>
@@ -2327,28 +2327,28 @@
         <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
         <v>3.15</v>
       </c>
       <c r="U12" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z12" t="n">
         <v>4.2</v>
@@ -2357,7 +2357,7 @@
         <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
         <v>2.7</v>
@@ -2366,13 +2366,13 @@
         <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>2.66</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
         <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.57</v>
+        <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
         <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
         <v>3.92</v>
@@ -2642,7 +2642,7 @@
         <v>4.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
         <v>2.31</v>
@@ -2654,25 +2654,25 @@
         <v>3.12</v>
       </c>
       <c r="U14" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
         <v>2.15</v>
@@ -2681,16 +2681,16 @@
         <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
         <v>1.74</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.5</v>
+        <v>4.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
         <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
         <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.19</v>
+        <v>1.66</v>
       </c>
       <c r="O16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.2</v>
       </c>
-      <c r="P16" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.73</v>
-      </c>
       <c r="U16" t="n">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="U17" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V17" t="n">
         <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
         <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,31 +3428,31 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="P19" t="n">
-        <v>5.51</v>
+        <v>4.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="R19" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="S19" t="n">
         <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W19" t="n">
         <v>1.14</v>
@@ -3461,28 +3461,28 @@
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA19" t="n">
         <v>1.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
         <v>2.21</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK19" t="n">
         <v>2.5</v>
@@ -3602,7 +3602,7 @@
         <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="T20" t="n">
         <v>2.65</v>
@@ -3617,13 +3617,13 @@
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
         <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
         <v>2.05</v>
@@ -3632,19 +3632,19 @@
         <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE20" t="n">
         <v>1.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3905,58 +3905,58 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O22" t="n">
         <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U22" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
         <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC22" t="n">
         <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF22" t="n">
         <v>1.99</v>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,52 +1997,52 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
         <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.85</v>
+        <v>4.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AD10" t="n">
         <v>1.44</v>
@@ -2051,10 +2051,10 @@
         <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,52 +2156,52 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="Q11" t="n">
         <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U11" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.57</v>
+        <v>3.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AD11" t="n">
         <v>1.44</v>
@@ -2210,10 +2210,10 @@
         <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>4.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.11</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="P14" t="n">
-        <v>4.81</v>
+        <v>4.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.09</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>4.52</v>
+        <v>4.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="R15" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.33</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AE15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>4.36</v>
+        <v>4.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.3</v>
       </c>
-      <c r="T16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AE16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="P17" t="n">
-        <v>4.7</v>
+        <v>4.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="U17" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.2</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.4</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.86</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>4.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="V19" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.82</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,43 +2633,43 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="V14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AA14" t="n">
         <v>1.9</v>
@@ -2678,19 +2678,19 @@
         <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="P15" t="n">
-        <v>4.36</v>
+        <v>4.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.95</v>
+        <v>4.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.11</v>
       </c>
-      <c r="AF15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,31 +2951,31 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>4.52</v>
+        <v>4.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
@@ -2984,31 +2984,31 @@
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
         <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="O17" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>4.81</v>
+        <v>4.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK17" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>4.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U18" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
         <v>2</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>4.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
         <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3905,37 +3905,37 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
         <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="R22" t="n">
         <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T22" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
         <v>3.15</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
         <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
         <v>1.36</v>
@@ -3956,7 +3956,7 @@
         <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF22" t="n">
         <v>1.99</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK22" t="n">
         <v>1.83</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,52 +1997,52 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
         <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U10" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.57</v>
+        <v>3.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AD10" t="n">
         <v>1.44</v>
@@ -2051,10 +2051,10 @@
         <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,52 +2156,52 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
         <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.85</v>
+        <v>4.57</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AD11" t="n">
         <v>1.44</v>
@@ -2210,10 +2210,10 @@
         <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>3.18</v>
+        <v>2.63</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.86</v>
+        <v>3.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,65 +2633,65 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.66</v>
+        <v>3.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="AE14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>4.95</v>
+        <v>4.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="R15" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="S15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.23</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z15" t="n">
-        <v>4.85</v>
+        <v>3.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>4.7</v>
+        <v>4.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="R16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
         <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.04</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AD16" t="n">
         <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="P17" t="n">
-        <v>4.36</v>
+        <v>4.81</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>4.81</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="R18" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
         <v>2</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="P19" t="n">
-        <v>4.52</v>
+        <v>4.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="R19" t="n">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="U19" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.42</v>
+        <v>4.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -725,46 +725,46 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R2" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="U2" t="n">
         <v>2.41</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
         <v>2.1</v>
@@ -776,13 +776,13 @@
         <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1043,22 +1043,22 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="P4" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="Q4" t="n">
         <v>2.9</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
         <v>3.6</v>
@@ -1067,19 +1067,19 @@
         <v>2.23</v>
       </c>
       <c r="V4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.53</v>
@@ -1088,13 +1088,13 @@
         <v>2.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF4" t="n">
         <v>1.44</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="O7" t="n">
-        <v>2.54</v>
+        <v>3.52</v>
       </c>
       <c r="P7" t="n">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>6.02</v>
       </c>
       <c r="O9" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
         <v>1.5</v>
@@ -1868,25 +1868,25 @@
         <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AB9" t="n">
         <v>2.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
         <v>1.15</v>
@@ -1895,7 +1895,7 @@
         <v>1.69</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="O10" t="n">
         <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
         <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,43 +2156,43 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O11" t="n">
         <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
         <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.57</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
         <v>1.65</v>
@@ -2201,19 +2201,19 @@
         <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF11" t="n">
         <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O12" t="n">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="P12" t="n">
-        <v>6.64</v>
+        <v>6.74</v>
       </c>
       <c r="Q12" t="n">
         <v>1.85</v>
@@ -2330,31 +2330,31 @@
         <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
         <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
         <v>2.15</v>
@@ -2369,7 +2369,7 @@
         <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
         <v>1.91</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
         <v>2.63</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2642,25 +2642,25 @@
         <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="R14" t="n">
         <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
         <v>3.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
@@ -2687,10 +2687,10 @@
         <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>4.52</v>
+        <v>5.51</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="R15" t="n">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.42</v>
+        <v>4.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>4.36</v>
+        <v>4.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.95</v>
+        <v>3.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
         <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O17" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="P17" t="n">
-        <v>4.81</v>
+        <v>5.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3278,13 +3278,13 @@
         <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="R18" t="n">
         <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T18" t="n">
         <v>3</v>
@@ -3293,34 +3293,34 @@
         <v>2.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
         <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
         <v>3.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AD18" t="n">
         <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
         <v>1.73</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
         <v>1.83</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="O19" t="n">
-        <v>4.15</v>
+        <v>3.74</v>
       </c>
       <c r="P19" t="n">
-        <v>4.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.61</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AB19" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O20" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="Q20" t="n">
         <v>3.1</v>
@@ -3602,28 +3602,28 @@
         <v>2.1</v>
       </c>
       <c r="S20" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U20" t="n">
         <v>2.99</v>
       </c>
       <c r="V20" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.99</v>
+        <v>3.13</v>
       </c>
       <c r="AA20" t="n">
         <v>2.05</v>
@@ -3632,19 +3632,19 @@
         <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
         <v>1.08</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="O21" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
         <v>3.28</v>
       </c>
-      <c r="P21" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P22" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="R22" t="n">
         <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="V22" t="n">
         <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB22" t="n">
         <v>1.61</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
         <v>1.06</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P8" t="n">
         <v>2.75</v>
       </c>
-      <c r="O8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.82</v>
-      </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2315,34 +2315,34 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="O12" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="P12" t="n">
         <v>6.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
         <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
         <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -2354,10 +2354,10 @@
         <v>4.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
         <v>2.7</v>
@@ -2366,13 +2366,13 @@
         <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.29</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z13" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>5.51</v>
+        <v>4.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="R15" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="S15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.23</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z15" t="n">
-        <v>4.85</v>
+        <v>3.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.43</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>4.52</v>
+        <v>5.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="AA16" t="n">
         <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>5.8</v>
+        <v>4.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>2.81</v>
+        <v>2.52</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AB18" t="n">
         <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,65 +3428,65 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.9</v>
+        <v>5.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="U19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.3</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="O20" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S20" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U20" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
         <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="AA20" t="n">
         <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.67</v>
+        <v>3.44</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.36</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3.52</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.97</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>2.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.66</v>
+        <v>5.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>2.27</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>3.36</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>3.52</v>
       </c>
       <c r="P8" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.01</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.56</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.43</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.27</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AB13" t="n">
         <v>1.95</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R14" t="n">
         <v>2.2</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.18</v>
+        <v>2.66</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>4.85</v>
+        <v>5.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE17" t="n">
+      <c r="AF17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.15</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.66</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC18" t="n">
-        <v>3.1</v>
+        <v>3.86</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.5</v>
       </c>
-      <c r="O19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.62</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1550,7 +1550,7 @@
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y7" t="n">
         <v>1.55</v>
@@ -1568,7 +1568,7 @@
         <v>5.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AE7" t="n">
         <v>1.02</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,65 +2633,65 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.91</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.52</v>
+        <v>5.51</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="R15" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.42</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>2.43</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.53</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.04</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AA16" t="n">
         <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.5</v>
       </c>
-      <c r="O17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.62</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.2</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V18" t="n">
+      <c r="AD18" t="n">
         <v>1.33</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>4.85</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.29</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="AE19" t="n">
         <v>1.09</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -725,34 +725,34 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="O2" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
         <v>3.75</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
@@ -761,28 +761,28 @@
         <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.88</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.58</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="AG7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.22</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.36</v>
+        <v>2.76</v>
       </c>
       <c r="O8" t="n">
-        <v>3.52</v>
+        <v>2.78</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.97</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.06</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.02</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
         <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.37</v>
+        <v>2.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.43</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.65</v>
+        <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V10" t="n">
         <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>1.54</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U11" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
         <v>1.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
         <v>1.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2360,10 +2360,10 @@
         <v>2.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
         <v>1.17</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.66</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC13" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
         <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,61 +2633,61 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.18</v>
+        <v>2.65</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.86</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
         <v>1.91</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.51</v>
+        <v>5.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.25</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="Z15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.14</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2960,13 +2960,13 @@
         <v>3.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
         <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
@@ -2975,16 +2975,16 @@
         <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
         <v>3.34</v>
@@ -2993,22 +2993,22 @@
         <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
         <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P17" t="n">
-        <v>4.85</v>
+        <v>5.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="U17" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.15</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>4.52</v>
+        <v>4.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R18" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
         <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>4.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V19" t="n">
         <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK19" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O20" t="n">
         <v>3.1</v>
@@ -3629,10 +3629,10 @@
         <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
         <v>1.29</v>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="O21" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.5</v>
       </c>
-      <c r="R21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.79</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.28</v>
+        <v>3.92</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3908,55 +3908,55 @@
         <v>1.87</v>
       </c>
       <c r="O22" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="R22" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S22" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="V22" t="n">
         <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AA22" t="n">
         <v>2.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF22" t="n">
         <v>1.91</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
         <v>1.85</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1052,25 +1052,25 @@
         <v>2.36</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
         <v>2.23</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -1079,28 +1079,28 @@
         <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA4" t="n">
         <v>1.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC4" t="n">
         <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF4" t="n">
         <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.53</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>3.08</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.47</v>
+        <v>4.05</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.06</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.05</v>
+        <v>2.47</v>
       </c>
       <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.17</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.14</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.45</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.41</v>
+        <v>1.54</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U10" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
         <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.15</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.54</v>
+        <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
         <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="R14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.93</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>5.6</v>
+        <v>4.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="U15" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V15" t="n">
         <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>5.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="U16" t="n">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.74</v>
+        <v>2.43</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O17" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>5.51</v>
+        <v>5.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.58</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.14</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK17" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC18" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AD18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,58 +3428,58 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
         <v>1.73</v>
@@ -3501,7 +3501,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="U7" t="n">
-        <v>4.05</v>
+        <v>2.47</v>
       </c>
       <c r="V7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.17</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.14</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.45</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="T8" t="n">
-        <v>3.08</v>
+        <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.47</v>
+        <v>4.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.06</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>1.54</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.54</v>
+        <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
         <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.41</v>
+        <v>1.54</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U11" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
         <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.15</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2</v>
+        <v>5.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.33</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.15</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.05</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>3.38</v>
       </c>
       <c r="AA14" t="n">
         <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,61 +2792,61 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="R15" t="n">
         <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
         <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG15" t="n">
         <v>2.1</v>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>5.51</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.05</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.43</v>
+        <v>1.74</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AC17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,58 +3428,58 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U19" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="V19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.4</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF19" t="n">
         <v>1.73</v>
@@ -3501,7 +3501,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>5.51</v>
+        <v>5.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.58</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.14</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK13" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AA14" t="n">
         <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.33</v>
+        <v>1.74</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,65 +2792,65 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC15" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AD15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
         <v>1.33</v>
@@ -2972,43 +2972,43 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="P17" t="n">
-        <v>4.2</v>
+        <v>5.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.33</v>
+        <v>1.87</v>
       </c>
       <c r="R17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.15</v>
       </c>
-      <c r="S17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.2</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2.1</v>
       </c>
-      <c r="S18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
         <v>1.85</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,61 +2633,61 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
         <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
         <v>2.1</v>
@@ -2706,7 +2706,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9</v>
+        <v>5.51</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.67</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="U15" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.09</v>
+        <v>1.47</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>2.43</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="O17" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>5.51</v>
+        <v>4.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="R17" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.95</v>
+        <v>3.34</v>
       </c>
       <c r="AA18" t="n">
         <v>1.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
         <v>2.1</v>
@@ -3342,7 +3342,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="R22" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="S22" t="n">
         <v>1.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U22" t="n">
         <v>3.22</v>
@@ -3932,7 +3932,7 @@
         <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
         <v>1.05</v>
@@ -3941,7 +3941,7 @@
         <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="AA22" t="n">
         <v>2.25</v>
@@ -3953,16 +3953,16 @@
         <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
         <v>1.01</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -725,25 +725,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="R2" t="n">
         <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
         <v>2.5</v>
@@ -761,28 +761,28 @@
         <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF2" t="n">
         <v>1.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK2" t="n">
         <v>1.2</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.18</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="S4" t="n">
         <v>1.2</v>
@@ -1064,43 +1064,43 @@
         <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
         <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
         <v>1.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD4" t="n">
         <v>1.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
         <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="AK4" t="n">
         <v>1.3</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1367,58 +1367,58 @@
         <v>2.88</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.47</v>
+        <v>3.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.98</v>
+        <v>2.31</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.66</v>
+        <v>5.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.78</v>
+        <v>3.64</v>
       </c>
       <c r="P8" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.57</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AB8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.25</v>
       </c>
-      <c r="U8" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.56</v>
+        <v>7.02</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T9" t="n">
         <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>2.88</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.41</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="R10" t="n">
         <v>2.3</v>
@@ -2015,46 +2015,46 @@
         <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U10" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
         <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.54</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.98</v>
+        <v>3.65</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="U11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.38</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
         <v>1.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O12" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P12" t="n">
-        <v>6.74</v>
+        <v>5.75</v>
       </c>
       <c r="Q12" t="n">
         <v>1.9</v>
@@ -2336,31 +2336,31 @@
         <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W12" t="n">
         <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AA12" t="n">
         <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="AD12" t="n">
         <v>1.38</v>
@@ -2369,10 +2369,10 @@
         <v>1.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK12" t="n">
         <v>2.64</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R13" t="n">
         <v>2.2</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.75</v>
       </c>
-      <c r="U13" t="n">
-        <v>2.9</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>1.85</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>2.33</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,65 +2633,65 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P14" t="n">
-        <v>4.1</v>
+        <v>5.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2.3</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,65 +2792,65 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>5.51</v>
+        <v>3.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG15" t="n">
         <v>2.05</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.43</v>
+        <v>1.74</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
         <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.38</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
         <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P17" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="R17" t="n">
         <v>2.15</v>
@@ -3143,13 +3143,13 @@
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
         <v>1.85</v>
@@ -3161,13 +3161,13 @@
         <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.4</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF18" t="n">
         <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>4.35</v>
+        <v>3.05</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R19" t="n">
         <v>2.1</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T19" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.09</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,19 +3587,19 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="R20" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S20" t="n">
         <v>1.37</v>
@@ -3617,28 +3617,28 @@
         <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
         <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF20" t="n">
         <v>1.77</v>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
         <v>1.44</v>
@@ -3746,19 +3746,19 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S21" t="n">
         <v>1.32</v>
@@ -3767,7 +3767,7 @@
         <v>2.92</v>
       </c>
       <c r="U21" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V21" t="n">
         <v>1.43</v>
@@ -3779,22 +3779,22 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
         <v>1.13</v>
@@ -3819,7 +3819,7 @@
         <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="P22" t="n">
         <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="R22" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
         <v>1.4</v>
@@ -3938,7 +3938,7 @@
         <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z22" t="n">
         <v>2.93</v>
@@ -3950,13 +3950,13 @@
         <v>1.66</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
         <v>1.95</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -746,13 +746,13 @@
         <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
@@ -764,19 +764,19 @@
         <v>4.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
         <v>1.62</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.19</v>
+        <v>1.81</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="S3" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="V3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="Q5" t="n">
         <v>3.1</v>
@@ -1217,10 +1217,10 @@
         <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U5" t="n">
         <v>4.33</v>
@@ -1235,16 +1235,16 @@
         <v>1.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AC5" t="n">
         <v>6.8</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>4.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="S6" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.35</v>
+        <v>6.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>2.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.15</v>
+        <v>2.96</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="U10" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
         <v>1.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P11" t="n">
-        <v>2.41</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.96</v>
+        <v>2.15</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="U11" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="V11" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
         <v>1.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="O13" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="P13" t="n">
-        <v>5.64</v>
+        <v>5.51</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.75</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.38</v>
+        <v>5.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.48</v>
       </c>
-      <c r="O14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.62</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.57</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P15" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF15" t="n">
         <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
         <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>4.35</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.23</v>
+        <v>2.67</v>
       </c>
       <c r="R17" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF17" t="n">
         <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O18" t="n">
         <v>3.8</v>
       </c>
       <c r="P18" t="n">
-        <v>4.6</v>
+        <v>5.64</v>
       </c>
       <c r="Q18" t="n">
         <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.29</v>
       </c>
-      <c r="T18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.75</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -714,14 +714,14 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46199.27083333334</v>
@@ -861,26 +861,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '85']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46199.29166666666</v>
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1039,32 +1039,32 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.64</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>3.47</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
         <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="U4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
         <v>1.6</v>
@@ -1076,40 +1076,40 @@
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z4" t="n">
         <v>4.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AC4" t="n">
         <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG4" t="n">
         <v>2.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '26', '40', '45+5']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '30']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46199.35763888889</v>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1198,32 +1198,32 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
         <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="P5" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="T5" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V5" t="n">
         <v>1.14</v>
@@ -1232,25 +1232,25 @@
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
         <v>1.73</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE5" t="n">
         <v>1.01</v>
@@ -1263,46 +1263,46 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46199.375</v>
@@ -1338,48 +1338,48 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
         <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
         <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.02</v>
+        <v>3.57</v>
       </c>
       <c r="R6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
         <v>4.1</v>
@@ -1391,77 +1391,77 @@
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>['33', '50', '81']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46199.41666666666</v>
@@ -1520,28 +1520,28 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.42</v>
+        <v>3.59</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>6.28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="S7" t="n">
         <v>1.57</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U7" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>1.2</v>
@@ -1550,34 +1550,34 @@
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1656,42 +1656,42 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
         <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
         <v>1.28</v>
@@ -1700,13 +1700,13 @@
         <v>3.14</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
@@ -1718,34 +1718,34 @@
         <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
         <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE8" t="n">
         <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '77', '90+9']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '31']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46199.5</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1830,42 +1830,42 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>6.39</v>
       </c>
       <c r="O9" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
         <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.02</v>
+        <v>6.08</v>
       </c>
       <c r="R9" t="n">
         <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
@@ -1877,25 +1877,25 @@
         <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
         <v>1.18</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1904,41 +1904,41 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80', '90']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.88</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46199.54166666666</v>
@@ -1974,130 +1974,130 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="R10" t="n">
         <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG10" t="n">
         <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '45+4']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '51', '58', '70']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46199.58333333334</v>
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2152,72 +2152,72 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="R11" t="n">
         <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T11" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB11" t="n">
         <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2229,34 +2229,34 @@
         <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46199.58333333334</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P12" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="Q12" t="n">
         <v>1.9</v>
@@ -2333,7 +2333,7 @@
         <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
         <v>2.4</v>
@@ -2342,37 +2342,37 @@
         <v>1.46</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
         <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="O13" t="n">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="P13" t="n">
-        <v>5.51</v>
+        <v>6.1</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.83</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AB13" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P14" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.2</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.62</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>5.54</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="O15" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
         <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
         <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.65</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3113,16 +3113,16 @@
         <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
         <v>3.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S17" t="n">
         <v>1.4</v>
@@ -3131,16 +3131,16 @@
         <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
         <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
         <v>1.36</v>
@@ -3149,13 +3149,13 @@
         <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
         <v>1.19</v>
@@ -3167,7 +3167,7 @@
         <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,16 +3269,16 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P18" t="n">
-        <v>5.64</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
         <v>2.2</v>
@@ -3287,46 +3287,46 @@
         <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.38</v>
+        <v>3.97</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>1.74</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,19 +3428,19 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S19" t="n">
         <v>1.33</v>
@@ -3449,43 +3449,43 @@
         <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,19 +3587,19 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O20" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S20" t="n">
         <v>1.37</v>
@@ -3626,7 +3626,7 @@
         <v>2.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
         <v>1.75</v>
@@ -3635,10 +3635,10 @@
         <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF20" t="n">
         <v>1.77</v>
@@ -3660,7 +3660,7 @@
         <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,19 +3746,19 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
         <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S21" t="n">
         <v>1.32</v>
@@ -3767,43 +3767,43 @@
         <v>2.92</v>
       </c>
       <c r="U21" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="O22" t="n">
         <v>2.98</v>
       </c>
       <c r="P22" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="R22" t="n">
         <v>2</v>
@@ -3923,10 +3923,10 @@
         <v>1.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U22" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="V22" t="n">
         <v>1.29</v>
@@ -3941,16 +3941,16 @@
         <v>1.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AA22" t="n">
         <v>2.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
         <v>1.18</v>
@@ -3962,7 +3962,7 @@
         <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,149 +1478,149 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>['1', '77', '90+9']</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>['21', '31']</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN7" t="n">
         <v>6</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46199.5</v>
@@ -1637,149 +1637,149 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="Q8" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.39</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>['1', '77', '90+9']</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>['21', '31']</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AN8" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AO8" t="n">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="AP8" t="n">
-        <v>24</v>
+        <v>-1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46199.5</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,31 +1965,31 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
         <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.94</v>
+        <v>2.39</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
         <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="U10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.07</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>['13', '45+4']</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>['17', '51', '58', '70']</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN10" t="n">
         <v>7</v>
       </c>
       <c r="AO10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AS10" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="AT10" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46199.58333333334</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,31 +2124,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,107 +2156,107 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
         <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.39</v>
+        <v>2.94</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
         <v>1.29</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>5.07</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['13', '45+4']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '51', '58', '70']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
         <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AS11" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AT11" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46199.58333333334</v>
@@ -2292,26 +2292,26 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '45+1', '87']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
@@ -2394,28 +2394,28 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46199.64583333334</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,19 +2442,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2463,118 +2463,118 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>6.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.09</v>
+        <v>2.72</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
         <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80', '87']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.42</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46199.65625</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,139 +2601,139 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="O14" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.45</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.25</v>
       </c>
-      <c r="T14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z14" t="n">
-        <v>5.54</v>
+        <v>3.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>['22', '56']</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46199.65625</v>
@@ -2760,139 +2760,139 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
+          <t>['6', '51']</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46199.65625</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
         <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,37 +3021,37 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP16" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46199.65625</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,139 +3078,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.94</v>
       </c>
       <c r="P17" t="n">
-        <v>3.05</v>
+        <v>6.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.72</v>
+        <v>2.09</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U17" t="n">
         <v>2.75</v>
       </c>
-      <c r="U17" t="n">
-        <v>2.95</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
         <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>['28', '90+2']</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>2.42</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46199.65625</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,139 +3237,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1.91</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB18" t="n">
         <v>2.4</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AC18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2.45</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '29']</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '63', '85']</t>
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.74</v>
+        <v>2.39</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO18" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46199.65625</v>
@@ -3405,13 +3405,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -3420,11 +3420,11 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AJ19" t="n">
@@ -3507,28 +3507,28 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP19" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU19" s="3" t="n">
         <v>46199.65625</v>
@@ -3564,26 +3564,26 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '89']</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -3666,28 +3666,28 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN20" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AU20" s="3" t="n">
         <v>46199.66666666666</v>

--- a/jogos_2026-06-26.xlsx
+++ b/jogos_2026-06-26.xlsx
@@ -1478,149 +1478,149 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.39</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>['1', '77', '90+9']</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>['21', '31']</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AO7" t="n">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="AP7" t="n">
-        <v>24</v>
+        <v>-1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46199.5</v>
@@ -1637,149 +1637,149 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['1', '77', '90+9']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>['21', '31']</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="n">
         <v>6</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46199.5</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,31 +1965,31 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
         <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.39</v>
+        <v>2.94</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
         <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>5.07</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['13', '45+4']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '51', '58', '70']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN10" t="n">
         <v>7</v>
       </c>
       <c r="AO10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AS10" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AT10" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46199.58333333334</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,31 +2124,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,107 +2156,107 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
         <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.94</v>
+        <v>2.39</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
         <v>1.29</v>
       </c>
       <c r="T11" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.07</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>['13', '45+4']</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>['17', '51', '58', '70']</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
         <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AS11" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="AT11" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46199.58333333334</v>
@@ -2442,31 +2442,31 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="U13" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
         <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>['80', '87']</t>
+          <t>['22', '56']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2556,25 +2556,25 @@
         <v>6</v>
       </c>
       <c r="AN13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.07</v>
+        <v>0.72</v>
       </c>
       <c r="AS13" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AT13" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46199.65625</v>
@@ -2601,28 +2601,28 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2633,68 +2633,68 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
         <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
         <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>['22', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -2703,37 +2703,37 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.74</v>
+        <v>2.11</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="AS14" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="AT14" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46199.65625</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,31 +2919,31 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2951,107 +2951,107 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.2</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.63</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.95</v>
+        <v>5.54</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.97</v>
+        <v>2.29</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '29']</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '63', '85']</t>
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.11</v>
+        <v>2.39</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AO16" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AP16" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.42</v>
+        <v>2.32</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.45</v>
+        <v>2.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="AT16" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46199.65625</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,139 +3078,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.94</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>6.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.09</v>
+        <v>2.72</v>
       </c>
       <c r="R17" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
         <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>['28', '90+2']</t>
+          <t>['80', '87']</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.42</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
         <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.79</v>
+        <v>1.07</v>
       </c>
       <c r="AS17" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="AT17" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46199.65625</v>
@@ -3237,31 +3237,31 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3269,107 +3269,107 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="P18" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="R18" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.25</v>
       </c>
-      <c r="T18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z18" t="n">
-        <v>5.54</v>
+        <v>3.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.29</v>
+        <v>3.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>['10', '29']</t>
+          <t>['28', '90+2']</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>['45+1', '63', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.32</v>
+        <v>1.54</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.14</v>
+        <v>0.79</v>
       </c>
       <c r="AS18" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AT18" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46199.65625</v>
@@ -3723,130 +3723,130 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P21" t="n">
         <v>3.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="S21" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
         <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '32', '68', '74', '90+4']</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '64']</t>
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN21" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO21" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP21" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU21" s="3" t="n">
         <v>46199.77083333334</v>
@@ -3882,36 +3882,36 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
         <v>2.98</v>
       </c>
       <c r="P22" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="Q22" t="n">
         <v>2.56</v>
@@ -3920,10 +3920,10 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T22" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
         <v>3.3</v>
@@ -3932,16 +3932,16 @@
         <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
         <v>1.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AA22" t="n">
         <v>2.25</v>
@@ -3950,7 +3950,7 @@
         <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="AD22" t="n">
         <v>1.18</v>
@@ -3966,46 +3966,46 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '90+4']</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AJ22" t="n">
         <v>1.24</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN22" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP22" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU22" s="3" t="n">
         <v>46199.79166666666</v>
